--- a/Excel_Practice_Files/All Practice Files.xlsx
+++ b/Excel_Practice_Files/All Practice Files.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cadd Mentor\Student_Class_Code\Jazaul_Hasan_Data_Anylytics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cadd Mentor\Student_Class_Code\Jazaul_Hasan_Data_Anylytics\Excel_Practice_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02BA023-3DB7-4B50-B3A1-1C6D77A30345}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECE26C6-202B-4245-8E82-CF5E13A7B179}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" tabRatio="797" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" tabRatio="797" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Day 1 Practice" sheetId="1" r:id="rId1"/>
@@ -3307,7 +3307,7 @@
     <col min="3" max="3" width="10.77734375" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -3349,13 +3349,7 @@
       <c r="E2" s="2">
         <v>47</v>
       </c>
-      <c r="F2" s="2">
-        <v>86</v>
-      </c>
-      <c r="G2">
-        <f t="shared" ref="G2:G8" si="0">SUM(B2:F2)</f>
-        <v>335</v>
-      </c>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -3373,13 +3367,7 @@
       <c r="E3" s="2">
         <v>77</v>
       </c>
-      <c r="F3" s="2">
-        <v>92</v>
-      </c>
-      <c r="G3">
-        <f t="shared" si="0"/>
-        <v>369</v>
-      </c>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -3397,13 +3385,7 @@
       <c r="E4" s="2">
         <v>72</v>
       </c>
-      <c r="F4" s="2">
-        <v>91</v>
-      </c>
-      <c r="G4">
-        <f t="shared" si="0"/>
-        <v>291</v>
-      </c>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -3421,13 +3403,7 @@
       <c r="E5" s="2">
         <v>91</v>
       </c>
-      <c r="F5" s="2">
-        <v>66</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="0"/>
-        <v>377</v>
-      </c>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -3445,13 +3421,7 @@
       <c r="E6" s="2">
         <v>57</v>
       </c>
-      <c r="F6" s="2">
-        <v>40</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="0"/>
-        <v>273</v>
-      </c>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -3469,13 +3439,7 @@
       <c r="E7" s="2">
         <v>57</v>
       </c>
-      <c r="F7" s="2">
-        <v>36</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="0"/>
-        <v>265</v>
-      </c>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -3493,13 +3457,7 @@
       <c r="E8" s="2">
         <v>33</v>
       </c>
-      <c r="F8" s="2">
-        <v>63</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="0"/>
-        <v>322</v>
-      </c>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="23"/>
@@ -4359,6 +4317,28 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
+      <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{3C27864C-F8AB-4AE2-9248-6AC71597E593}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Day 2 Practice'!B2:E2</xm:f>
+              <xm:sqref>F2</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+      </x14:sparklineGroups>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
